--- a/results/04_final_refined_daily_hydroclimate_data/203/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Avg_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -26,6 +26,9 @@
   </si>
   <si>
     <t>Avg_Temperature</t>
+  </si>
+  <si>
+    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -411,7 +414,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -452,8 +455,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5">
-        <v>27</v>
+      <c r="D5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -537,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -551,7 +554,7 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -579,7 +582,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>28.5</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -691,7 +694,7 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>23.2</v>
+        <v>25.2</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -719,7 +722,7 @@
         <v>23</v>
       </c>
       <c r="D24">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -817,7 +820,7 @@
         <v>30</v>
       </c>
       <c r="D31">
-        <v>24.7</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -957,7 +960,7 @@
         <v>9</v>
       </c>
       <c r="D41">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -971,7 +974,7 @@
         <v>10</v>
       </c>
       <c r="D42">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1083,7 +1086,7 @@
         <v>18</v>
       </c>
       <c r="D50">
-        <v>28.1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1097,7 +1100,7 @@
         <v>19</v>
       </c>
       <c r="D51">
-        <v>26.8</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1111,7 +1114,7 @@
         <v>20</v>
       </c>
       <c r="D52">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="53" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Avg_Temperature_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Avg_Temperature_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Avg_Temperature</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -414,7 +411,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -455,8 +452,8 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" t="s">
-        <v>4</v>
+      <c r="D5">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1086,7 +1083,7 @@
         <v>18</v>
       </c>
       <c r="D50">
-        <v>26</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="51" spans="1:4">
